--- a/docs/dashboard/data/데이터변경이력.xlsx
+++ b/docs/dashboard/data/데이터변경이력.xlsx
@@ -98,7 +98,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J192"/>
+  <dimension ref="A1:J213"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="20.0" customWidth="true"/>
@@ -168,27 +168,27 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 13:46:39</t>
+          <t>2026-09-10 10:41:23</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>디지트론</t>
+          <t>주식회사 카프마이크로</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>정재종</t>
+          <t>박준영</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>jjjeong@digitron.kr</t>
+          <t>jypark@caphmicro.com</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>계측기 통합 대장</t>
+          <t>반·출입 관리</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -198,7 +198,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>DT-T-01-0012 DC POWER SUPPLY</t>
+          <t>CM-0015 휘도계</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -213,138 +213,138 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>반출 등록</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 13:41:35</t>
+          <t>2026-09-08 13:37:41</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>디지트론</t>
+          <t>(주)케이피씨엠</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>정재종</t>
+          <t>이예슬</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>jjjeong@digitron.kr</t>
+          <t>ys-lee@kpccorp.co.kr</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>계측기 통합 대장</t>
+          <t>교정 접수 관리</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>DT-T-01-0011 DC POWER SUPPLY</t>
+          <t>CW26003961</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>계측기 삭제</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>Thread plug gauge</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 13:40:51</t>
+          <t>2026-09-08 13:37:41</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>디지트론</t>
+          <t>(주)케이피씨엠</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>정재종</t>
+          <t>이예슬</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>jjjeong@digitron.kr</t>
+          <t>ys-lee@kpccorp.co.kr</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>계측기 통합 대장</t>
+          <t>교정 접수 관리</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>DT-T-01-0010 DC POWER SUPPLY</t>
+          <t>CW26003961</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>계측기 삭제</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>Thread plug gauge</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 13:38:11</t>
+          <t>2026-09-08 13:37:41</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>디지트론</t>
+          <t>(주)케이피씨엠</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>정재종</t>
+          <t>이예슬</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>jjjeong@digitron.kr</t>
+          <t>ys-lee@kpccorp.co.kr</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>계측기 통합 대장</t>
+          <t>교정 접수 관리</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -354,49 +354,49 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>DT-T-01-0009 DC POWER SUPPLY</t>
+          <t>CW26003961</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>사용 부서</t>
+          <t>계측기 삭제</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>Thread plug gauge</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>연구2팀</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 13:38:11</t>
+          <t>2026-09-08 13:37:41</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>디지트론</t>
+          <t>(주)케이피씨엠</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>정재종</t>
+          <t>이예슬</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>jjjeong@digitron.kr</t>
+          <t>ys-lee@kpccorp.co.kr</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>계측기 통합 대장</t>
+          <t>교정 접수 관리</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -406,49 +406,49 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>DT-T-01-0009 DC POWER SUPPLY</t>
+          <t>CW26003961</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>담당자</t>
+          <t>계측기 삭제</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>Thread plug gauge</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>한철희</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 13:38:11</t>
+          <t>2026-09-08 13:37:41</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>디지트론</t>
+          <t>(주)케이피씨엠</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>정재종</t>
+          <t>이예슬</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>jjjeong@digitron.kr</t>
+          <t>ys-lee@kpccorp.co.kr</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>계측기 통합 대장</t>
+          <t>교정 접수 관리</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -458,49 +458,49 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>DT-T-01-0009 DC POWER SUPPLY</t>
+          <t>CW26003961</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>부담당자</t>
+          <t>OUTSIDE MICROMETER 성적서 언어</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>국영문</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>임영웅</t>
+          <t>영문</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 13:37:35</t>
+          <t>2026-09-08 13:37:41</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>디지트론</t>
+          <t>(주)케이피씨엠</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>정재종</t>
+          <t>이예슬</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>jjjeong@digitron.kr</t>
+          <t>ys-lee@kpccorp.co.kr</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>계측기 통합 대장</t>
+          <t>교정 접수 관리</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -510,49 +510,49 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>DT-T-01-0008 DC POWER SUPPLY</t>
+          <t>CW26003961</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>사용 부서</t>
+          <t>R-게이지 성적서 언어</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>국영문</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>연구5팀</t>
+          <t>영문</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 13:37:35</t>
+          <t>2026-09-08 13:37:41</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>디지트론</t>
+          <t>(주)케이피씨엠</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>정재종</t>
+          <t>이예슬</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>jjjeong@digitron.kr</t>
+          <t>ys-lee@kpccorp.co.kr</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>계측기 통합 대장</t>
+          <t>교정 접수 관리</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -562,49 +562,49 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>DT-T-01-0008 DC POWER SUPPLY</t>
+          <t>CW26003961</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>담당자</t>
+          <t>R-게이지 성적서 언어</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>국영문</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>최익수</t>
+          <t>영문</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 13:37:35</t>
+          <t>2026-09-08 13:37:41</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>디지트론</t>
+          <t>(주)케이피씨엠</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>정재종</t>
+          <t>이예슬</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>jjjeong@digitron.kr</t>
+          <t>ys-lee@kpccorp.co.kr</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>계측기 통합 대장</t>
+          <t>교정 접수 관리</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -614,49 +614,49 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>DT-T-01-0008 DC POWER SUPPLY</t>
+          <t>CW26003961</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>부담당자</t>
+          <t>R-게이지 성적서 언어</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>국영문</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>최용우</t>
+          <t>영문</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 13:36:50</t>
+          <t>2026-09-08 13:37:41</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>디지트론</t>
+          <t>(주)케이피씨엠</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>정재종</t>
+          <t>이예슬</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>jjjeong@digitron.kr</t>
+          <t>ys-lee@kpccorp.co.kr</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>계측기 통합 대장</t>
+          <t>교정 접수 관리</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -666,49 +666,49 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>DT-T-01-0007 DC POWER SUPPLY</t>
+          <t>CW26003961</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>사용 부서</t>
+          <t>회전형 풍속계 성적서 언어</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>국영문</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>연구6팀</t>
+          <t>영문</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 13:36:50</t>
+          <t>2026-09-08 13:37:41</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>디지트론</t>
+          <t>(주)케이피씨엠</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>정재종</t>
+          <t>이예슬</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>jjjeong@digitron.kr</t>
+          <t>ys-lee@kpccorp.co.kr</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>계측기 통합 대장</t>
+          <t>교정 접수 관리</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -718,44 +718,44 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>DT-T-01-0007 DC POWER SUPPLY</t>
+          <t>CW26003961</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>담당자</t>
+          <t>Vnotch 확인용 Film 성적서 언어</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>국영문</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>임정우</t>
+          <t>영문</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 13:36:50</t>
+          <t>2026-09-08 08:33:07</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>디지트론</t>
+          <t>(주)케이피씨엠</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>정재종</t>
+          <t>이예슬</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>jjjeong@digitron.kr</t>
+          <t>ys-lee@kpccorp.co.kr</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -770,44 +770,44 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>DT-T-01-0007 DC POWER SUPPLY</t>
+          <t>Thread plug gauge</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>부담당자</t>
+          <t>교정 주기</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>12개월</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>김한위</t>
+          <t>24개월</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 13:03:32</t>
+          <t>2026-09-08 08:32:59</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>디지트론</t>
+          <t>(주)케이피씨엠</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>정재종</t>
+          <t>이예슬</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>jjjeong@digitron.kr</t>
+          <t>ys-lee@kpccorp.co.kr</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -822,44 +822,44 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>DT-T-01-0006 DC POWER SUPPLY</t>
+          <t>Thread plug gauge</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>사용 부서</t>
+          <t>교정 주기</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>12개월</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>연구1팀</t>
+          <t>24개월</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 13:03:32</t>
+          <t>2026-09-08 08:32:52</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>디지트론</t>
+          <t>(주)케이피씨엠</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>정재종</t>
+          <t>이예슬</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>jjjeong@digitron.kr</t>
+          <t>ys-lee@kpccorp.co.kr</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -874,44 +874,44 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>DT-T-01-0006 DC POWER SUPPLY</t>
+          <t>Thread plug gauge</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>담당자</t>
+          <t>교정 주기</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>12개월</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>송종문</t>
+          <t>24개월</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 13:03:32</t>
+          <t>2026-09-08 08:32:39</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>디지트론</t>
+          <t>(주)케이피씨엠</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>정재종</t>
+          <t>이예슬</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>jjjeong@digitron.kr</t>
+          <t>ys-lee@kpccorp.co.kr</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -926,64 +926,64 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>DT-T-01-0006 DC POWER SUPPLY</t>
+          <t>Thread plug gauge</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>부담당자</t>
+          <t>교정 주기</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>12개월</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>나동욱</t>
+          <t>24개월</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 11:56:23</t>
+          <t>2026-09-08 08:32:18</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>디지트론</t>
+          <t>(주)케이피씨엠</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>정재종</t>
+          <t>이예슬</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>jjjeong@digitron.kr</t>
+          <t>ys-lee@kpccorp.co.kr</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>계측기 통합 대장</t>
+          <t>교정 접수 관리</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>DT-T-01-0009 DC POWER SUPPLY</t>
+          <t>CW26003961</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>Thread plug gauge 요청사항</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -993,49 +993,49 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>교정주기 2년</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 11:55:28</t>
+          <t>2026-09-08 08:32:18</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>디지트론</t>
+          <t>(주)케이피씨엠</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>정재종</t>
+          <t>이예슬</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>jjjeong@digitron.kr</t>
+          <t>ys-lee@kpccorp.co.kr</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>계측기 통합 대장</t>
+          <t>교정 접수 관리</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>DT-T-01-0008 DC POWER SUPPLY</t>
+          <t>CW26003961</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>Thread plug gauge 요청사항</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1045,49 +1045,49 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>교정주기 2년</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 11:54:21</t>
+          <t>2026-09-08 08:32:18</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>디지트론</t>
+          <t>(주)케이피씨엠</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>정재종</t>
+          <t>이예슬</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>jjjeong@digitron.kr</t>
+          <t>ys-lee@kpccorp.co.kr</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>계측기 통합 대장</t>
+          <t>교정 접수 관리</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>DT-T-01-0007 DC POWER SUPPLY</t>
+          <t>CW26003961</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>Thread plug gauge 요청사항</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1097,49 +1097,49 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>교정주기 2년</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 11:53:04</t>
+          <t>2026-09-08 08:32:18</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>디지트론</t>
+          <t>(주)케이피씨엠</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>정재종</t>
+          <t>이예슬</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>jjjeong@digitron.kr</t>
+          <t>ys-lee@kpccorp.co.kr</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>계측기 통합 대장</t>
+          <t>교정 접수 관리</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>DT-T-01-0006 DC POWER SUPPLY</t>
+          <t>CW26003961</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>Thread plug gauge 요청사항</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1149,34 +1149,34 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>교정주기 2년</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 11:47:58</t>
+          <t>2026-09-07 10:58:55</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>디지트론</t>
+          <t>(주)케이피씨엠</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>정재종</t>
+          <t>이예슬</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>jjjeong@digitron.kr</t>
+          <t>ys-lee@kpccorp.co.kr</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>계측기 통합 대장</t>
+          <t>교정 접수 관리</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>DT-T-01-0005 DC POWER SUPPLY</t>
+          <t>CW26003962</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1201,34 +1201,34 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>교정 접수 등록</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 11:46:53</t>
+          <t>2026-09-07 10:54:19</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>디지트론</t>
+          <t>(주)케이피씨엠</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>정재종</t>
+          <t>이예슬</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>jjjeong@digitron.kr</t>
+          <t>ys-lee@kpccorp.co.kr</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>계측기 통합 대장</t>
+          <t>교정 접수 관리</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>DT-T-01-0002 DC POWER SUPPLY</t>
+          <t>CW26003961</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1253,14 +1253,14 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>교정 접수 등록</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 11:10:02</t>
+          <t>2026-09-01 13:46:39</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>DT-T-01-0001 DC POWER SUPPLY</t>
+          <t>DT-T-01-0012 DC POWER SUPPLY</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1312,22 +1312,22 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31 11:59:33</t>
+          <t>2026-09-01 13:41:35</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t>디지트론</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>김호영</t>
+          <t>정재종</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>hoykim@caphmicro.com</t>
+          <t>jjjeong@digitron.kr</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1337,17 +1337,17 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>수정</t>
+          <t>등록</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>CM-0022 광 측정기</t>
+          <t>DT-T-01-0011 DC POWER SUPPLY</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>비고</t>
+          <t/>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1357,29 +1357,29 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>민감장비로 현장보관</t>
+          <t>계측기 등록</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31 11:59:12</t>
+          <t>2026-09-01 13:40:51</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t>디지트론</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>김호영</t>
+          <t>정재종</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>hoykim@caphmicro.com</t>
+          <t>jjjeong@digitron.kr</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1389,17 +1389,17 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>수정</t>
+          <t>등록</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>CM-0033 CABLE&amp;HARNESS MULTI TESTER</t>
+          <t>DT-T-01-0010 DC POWER SUPPLY</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>비고</t>
+          <t/>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1409,29 +1409,29 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>민감장비로 현장 보관</t>
+          <t>계측기 등록</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31 11:58:01</t>
+          <t>2026-09-01 13:38:11</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t>디지트론</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>김호영</t>
+          <t>정재종</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>hoykim@caphmicro.com</t>
+          <t>jjjeong@digitron.kr</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1446,44 +1446,44 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>CM-0010 온도측정기</t>
+          <t>DT-T-01-0009 DC POWER SUPPLY</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t>사용 부서</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t/>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>미사용</t>
+          <t>연구2팀</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27 15:25:47</t>
+          <t>2026-09-01 13:38:11</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t>디지트론</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>김호영</t>
+          <t>정재종</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>hoykim@caphmicro.com</t>
+          <t>jjjeong@digitron.kr</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1498,44 +1498,44 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>CM-TL-0223 Optiocal Laser Source</t>
+          <t>DT-T-01-0009 DC POWER SUPPLY</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>모델</t>
+          <t>담당자</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>LOS-36V2</t>
+          <t/>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>OLS-36V2</t>
+          <t>한철희</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:08:59</t>
+          <t>2026-09-01 13:38:11</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t>디지트론</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>김호영</t>
+          <t>정재종</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>hoykim@caphmicro.com</t>
+          <t>jjjeong@digitron.kr</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1545,17 +1545,17 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>CM-TL-0224 Optical Power Meter</t>
+          <t>DT-T-01-0009 DC POWER SUPPLY</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>부담당자</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1565,29 +1565,29 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>임영웅</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:07:31</t>
+          <t>2026-09-01 13:37:35</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t>디지트론</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>김호영</t>
+          <t>정재종</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>hoykim@caphmicro.com</t>
+          <t>jjjeong@digitron.kr</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1597,17 +1597,17 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>CM-TL-0223 Optiocal Laser Source</t>
+          <t>DT-T-01-0008 DC POWER SUPPLY</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>사용 부서</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -1617,49 +1617,49 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>연구5팀</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 08:11:42</t>
+          <t>2026-09-01 13:37:35</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>(주)신화프리텍</t>
+          <t>디지트론</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>최문정</t>
+          <t>정재종</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>mjchoi@shinhwa-pritech.com</t>
+          <t>jjjeong@digitron.kr</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>사용자 관리</t>
+          <t>계측기 통합 대장</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>김혜민</t>
+          <t>DT-T-01-0008 DC POWER SUPPLY</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>담당자</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1669,29 +1669,29 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>사용자 등록</t>
+          <t>최익수</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 09:56:13</t>
+          <t>2026-09-01 13:37:35</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>에브제트아시아(주)</t>
+          <t>디지트론</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>전승헌</t>
+          <t>정재종</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>sh.chun@avjet.kr</t>
+          <t>jjjeong@digitron.kr</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1706,44 +1706,44 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>125 KIT STRUT SERVICE</t>
+          <t>DT-T-01-0008 DC POWER SUPPLY</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>설치 위치</t>
+          <t>부담당자</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t/>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>FIC &gt; 1호기 &gt; 장비실 &gt; J3</t>
+          <t>최용우</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 09:50:47</t>
+          <t>2026-09-01 13:36:50</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>에브제트아시아(주)</t>
+          <t>디지트론</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>전승헌</t>
+          <t>정재종</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>sh.chun@avjet.kr</t>
+          <t>jjjeong@digitron.kr</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1758,12 +1758,12 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>125 KIT STRUT SERVICE</t>
+          <t>DT-T-01-0007 DC POWER SUPPLY</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>설치 위치</t>
+          <t>사용 부서</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -1773,29 +1773,29 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>연구6팀</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 09:45:48</t>
+          <t>2026-09-01 13:36:50</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>에브제트아시아(주)</t>
+          <t>디지트론</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>전승헌</t>
+          <t>정재종</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>sh.chun@avjet.kr</t>
+          <t>jjjeong@digitron.kr</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1805,17 +1805,17 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>125 KIT STRUT SERVICE</t>
+          <t>DT-T-01-0007 DC POWER SUPPLY</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>담당자</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -1825,49 +1825,49 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>임정우</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:48:49</t>
+          <t>2026-09-01 13:36:50</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t>디지트론</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>박준영</t>
+          <t>정재종</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>jypark@caphmicro.com</t>
+          <t>jjjeong@digitron.kr</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>사용자 관리</t>
+          <t>계측기 통합 대장</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>김호영</t>
+          <t>DT-T-01-0007 DC POWER SUPPLY</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>부담당자</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -1877,29 +1877,29 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>사용자 등록</t>
+          <t>김한위</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:35:09</t>
+          <t>2026-09-01 13:03:32</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t>디지트론</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>박준영</t>
+          <t>정재종</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>jypark@caphmicro.com</t>
+          <t>jjjeong@digitron.kr</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1914,44 +1914,44 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>CM-0047 디지털 게이지</t>
+          <t>DT-T-01-0006 DC POWER SUPPLY</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>모델</t>
+          <t>사용 부서</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>33574</t>
+          <t/>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>ID-C1012</t>
+          <t>연구1팀</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:13:35</t>
+          <t>2026-09-01 13:03:32</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t>디지트론</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>박준영</t>
+          <t>정재종</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>jypark@caphmicro.com</t>
+          <t>jjjeong@digitron.kr</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1966,44 +1966,44 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>CM-0060 Digital Push Pull Gage</t>
+          <t>DT-T-01-0006 DC POWER SUPPLY</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t>담당자</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t/>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>미사용</t>
+          <t>송종문</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:13:28</t>
+          <t>2026-09-01 13:03:32</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t>디지트론</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>박준영</t>
+          <t>정재종</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>jypark@caphmicro.com</t>
+          <t>jjjeong@digitron.kr</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2018,44 +2018,44 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>CM-0059 Digital Push Pull Gage</t>
+          <t>DT-T-01-0006 DC POWER SUPPLY</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t>부담당자</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t/>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>미사용</t>
+          <t>나동욱</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:13:21</t>
+          <t>2026-09-01 11:56:23</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t>디지트론</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>박준영</t>
+          <t>정재종</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>jypark@caphmicro.com</t>
+          <t>jjjeong@digitron.kr</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2065,49 +2065,49 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>수정</t>
+          <t>등록</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>CM-0058 Digital Push Pull Gage</t>
+          <t>DT-T-01-0009 DC POWER SUPPLY</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t/>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t/>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>미사용</t>
+          <t>계측기 등록</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:13:11</t>
+          <t>2026-09-01 11:55:28</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t>디지트론</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>박준영</t>
+          <t>정재종</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>jypark@caphmicro.com</t>
+          <t>jjjeong@digitron.kr</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2117,49 +2117,49 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>수정</t>
+          <t>등록</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>CM-0056 인두팁 온도계</t>
+          <t>DT-T-01-0008 DC POWER SUPPLY</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t/>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t/>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>미사용</t>
+          <t>계측기 등록</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:13:03</t>
+          <t>2026-09-01 11:54:21</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t>디지트론</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>박준영</t>
+          <t>정재종</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>jypark@caphmicro.com</t>
+          <t>jjjeong@digitron.kr</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2169,49 +2169,49 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>수정</t>
+          <t>등록</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>CM-0055 디지털테스터</t>
+          <t>DT-T-01-0007 DC POWER SUPPLY</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t/>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t/>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>미사용</t>
+          <t>계측기 등록</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:12:54</t>
+          <t>2026-09-01 11:53:04</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t>디지트론</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>박준영</t>
+          <t>정재종</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>jypark@caphmicro.com</t>
+          <t>jjjeong@digitron.kr</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2221,49 +2221,49 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>수정</t>
+          <t>등록</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>CM-0053 전자기 방사선 측정기</t>
+          <t>DT-T-01-0006 DC POWER SUPPLY</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t/>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t/>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>미사용</t>
+          <t>계측기 등록</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:12:47</t>
+          <t>2026-09-01 11:47:58</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t>디지트론</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>박준영</t>
+          <t>정재종</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>jypark@caphmicro.com</t>
+          <t>jjjeong@digitron.kr</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2273,49 +2273,49 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>수정</t>
+          <t>등록</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>CM-0052 Cable Tester and Digital Multimeter</t>
+          <t>DT-T-01-0005 DC POWER SUPPLY</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t/>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t/>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>미사용</t>
+          <t>계측기 등록</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:12:39</t>
+          <t>2026-09-01 11:46:53</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t>디지트론</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>박준영</t>
+          <t>정재종</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>jypark@caphmicro.com</t>
+          <t>jjjeong@digitron.kr</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2325,49 +2325,49 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>수정</t>
+          <t>등록</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>CM-0051 휴대용 소음 감지기</t>
+          <t>DT-T-01-0002 DC POWER SUPPLY</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t/>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t/>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>미사용</t>
+          <t>계측기 등록</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:12:31</t>
+          <t>2026-09-01 11:10:02</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t>디지트론</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>박준영</t>
+          <t>정재종</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>jypark@caphmicro.com</t>
+          <t>jjjeong@digitron.kr</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2377,34 +2377,34 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>수정</t>
+          <t>등록</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>CM-0050 Digital Push Pull Gage</t>
+          <t>DT-T-01-0001 DC POWER SUPPLY</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t/>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t/>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>미사용</t>
+          <t>계측기 등록</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:12:23</t>
+          <t>2026-08-31 11:59:33</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2414,12 +2414,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>박준영</t>
+          <t>김호영</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>jypark@caphmicro.com</t>
+          <t>hoykim@caphmicro.com</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2434,29 +2434,29 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>CM-0049 버니어켈리퍼스</t>
+          <t>CM-0022 광 측정기</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t>비고</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t/>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>미사용</t>
+          <t>민감장비로 현장보관</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:12:16</t>
+          <t>2026-08-31 11:59:12</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2466,12 +2466,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>박준영</t>
+          <t>김호영</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>jypark@caphmicro.com</t>
+          <t>hoykim@caphmicro.com</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2486,29 +2486,29 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>CM-0048 디지털 토크 드라이버 셋트</t>
+          <t>CM-0033 CABLE&amp;HARNESS MULTI TESTER</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t>비고</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t/>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>미사용</t>
+          <t>민감장비로 현장 보관</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:12:09</t>
+          <t>2026-08-31 11:58:01</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>박준영</t>
+          <t>김호영</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>jypark@caphmicro.com</t>
+          <t>hoykim@caphmicro.com</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>CM-0047 디지털 게이지</t>
+          <t>CM-0010 온도측정기</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2560,7 +2560,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:12:01</t>
+          <t>2026-08-27 15:25:47</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>박준영</t>
+          <t>김호영</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>jypark@caphmicro.com</t>
+          <t>hoykim@caphmicro.com</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2590,29 +2590,29 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>CM-0046 Milliohm Meter</t>
+          <t>CM-TL-0223 Optiocal Laser Source</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t>모델</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>LOS-36V2</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>미사용</t>
+          <t>OLS-36V2</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:11:53</t>
+          <t>2026-08-26 16:08:59</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>박준영</t>
+          <t>김호영</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>jypark@caphmicro.com</t>
+          <t>hoykim@caphmicro.com</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2637,34 +2637,34 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>수정</t>
+          <t>등록</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>CM-0045 전자저울</t>
+          <t>CM-TL-0224 Optical Power Meter</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t/>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t/>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>미사용</t>
+          <t>계측기 등록</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:11:44</t>
+          <t>2026-08-26 16:07:31</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>박준영</t>
+          <t>김호영</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>jypark@caphmicro.com</t>
+          <t>hoykim@caphmicro.com</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -2689,101 +2689,101 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>수정</t>
+          <t>등록</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>CM-0044 Force Gauge</t>
+          <t>CM-TL-0223 Optiocal Laser Source</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t/>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t/>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>미사용</t>
+          <t>계측기 등록</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:11:17</t>
+          <t>2026-08-21 08:11:42</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t>(주)신화프리텍</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>박준영</t>
+          <t>최문정</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>jypark@caphmicro.com</t>
+          <t>mjchoi@shinhwa-pritech.com</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>계측기 통합 대장</t>
+          <t>사용자 관리</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>수정</t>
+          <t>등록</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>CM-0043 Digital Push Pull Gage</t>
+          <t>김혜민</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t/>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t/>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>미사용</t>
+          <t>사용자 등록</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:11:06</t>
+          <t>2026-08-19 09:56:13</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t>에브제트아시아(주)</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>박준영</t>
+          <t>전승헌</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>jypark@caphmicro.com</t>
+          <t>sh.chun@avjet.kr</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -2798,44 +2798,44 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>CM-0033 CABLE&amp;HARNESS MULTI TESTER</t>
+          <t>125 KIT STRUT SERVICE</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t>설치 위치</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>FIC</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>미사용</t>
+          <t>FIC &gt; 1호기 &gt; 장비실 &gt; J3</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:10:44</t>
+          <t>2026-08-19 09:50:47</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t>에브제트아시아(주)</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>박준영</t>
+          <t>전승헌</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>jypark@caphmicro.com</t>
+          <t>sh.chun@avjet.kr</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2850,44 +2850,44 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>CM-0022 광 측정기</t>
+          <t>125 KIT STRUT SERVICE</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t>설치 위치</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t/>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>미사용</t>
+          <t>J3</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:10:25</t>
+          <t>2026-08-19 09:45:48</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t>에브제트아시아(주)</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>박준영</t>
+          <t>전승헌</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>jypark@caphmicro.com</t>
+          <t>sh.chun@avjet.kr</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -2897,34 +2897,34 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>수정</t>
+          <t>등록</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>CM-0042 HiTESTER</t>
+          <t>125 KIT STRUT SERVICE</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t/>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t/>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>미사용</t>
+          <t>계측기 등록</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:09:52</t>
+          <t>2026-08-18 11:48:49</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>계측기 통합 대장</t>
+          <t>사용자 관리</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>CM-0060 Digital Push Pull Gage</t>
+          <t>김호영</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2969,14 +2969,14 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>사용자 등록</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:09:03</t>
+          <t>2026-08-18 11:35:09</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3001,34 +3001,34 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>CM-0059 Digital Push Pull Gage</t>
+          <t>CM-0047 디지털 게이지</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>모델</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>33574</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>ID-C1012</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:08:31</t>
+          <t>2026-08-18 11:13:35</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3053,34 +3053,34 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>CM-0058 Digital Push Pull Gage</t>
+          <t>CM-0060 Digital Push Pull Gage</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>상태</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>정상</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>미사용</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:07:55</t>
+          <t>2026-08-18 11:13:28</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3105,34 +3105,34 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>CM-0057 버니어켈리퍼스</t>
+          <t>CM-0059 Digital Push Pull Gage</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>상태</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>정상</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>미사용</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:07:55</t>
+          <t>2026-08-18 11:13:21</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3157,34 +3157,34 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>CM-0057 버니어켈리퍼스</t>
+          <t>CM-0058 Digital Push Pull Gage</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>첨부 추가</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>정상</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>CM-0057_내외측 켈리퍼(Digamatic Calipers)_251203_대전연구소(25016231-1)_적합성.pdf</t>
+          <t>미사용</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:07:55</t>
+          <t>2026-08-18 11:13:11</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3209,34 +3209,34 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>CM-0057 버니어켈리퍼스</t>
+          <t>CM-0056 인두팁 온도계</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>첨부 추가</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>정상</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>CM-0057_내외측 켈리퍼(Digamatic Calipers)_251203_대전연구소(25016231-1).pdf</t>
+          <t>미사용</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:59:48</t>
+          <t>2026-08-18 11:13:03</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3261,34 +3261,34 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>CM-0056 인두팁 온도계</t>
+          <t>CM-0055 디지털테스터</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>상태</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>정상</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>미사용</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:58:52</t>
+          <t>2026-08-18 11:12:54</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3313,34 +3313,34 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>CM-0055 디지털테스터</t>
+          <t>CM-0053 전자기 방사선 측정기</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>상태</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>정상</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>미사용</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:58:01</t>
+          <t>2026-08-18 11:12:47</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3365,34 +3365,34 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>CM-0054 토크 드라이버</t>
+          <t>CM-0052 Cable Tester and Digital Multimeter</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>상태</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>정상</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>미사용</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:58:01</t>
+          <t>2026-08-18 11:12:39</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3417,34 +3417,34 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>CM-0054 토크 드라이버</t>
+          <t>CM-0051 휴대용 소음 감지기</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>첨부 추가</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>정상</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>관리번호 CM-0054 260306 - 토크드라이버(457749Q)_연구개발_적합성.pdf</t>
+          <t>미사용</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:58:01</t>
+          <t>2026-08-18 11:12:31</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3469,34 +3469,34 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>CM-0054 토크 드라이버</t>
+          <t>CM-0050 Digital Push Pull Gage</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>첨부 추가</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>정상</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>관리번호 CM-0054 260306 - 토크드라이버(457749Q)_연구개발.pdf</t>
+          <t>미사용</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:57:01</t>
+          <t>2026-08-18 11:12:23</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3521,34 +3521,34 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>CM-0053 전자기 방사선 측정기</t>
+          <t>CM-0049 버니어켈리퍼스</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>상태</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>정상</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>미사용</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:56:19</t>
+          <t>2026-08-18 11:12:16</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3573,34 +3573,34 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>CM-0052 Cable Tester and Digital Multimeter</t>
+          <t>CM-0048 디지털 토크 드라이버 셋트</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>상태</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>정상</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>미사용</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:55:45</t>
+          <t>2026-08-18 11:12:09</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3625,34 +3625,34 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>CM-0051 휴대용 소음 감지기</t>
+          <t>CM-0047 디지털 게이지</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>상태</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>정상</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>미사용</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:33:45</t>
+          <t>2026-08-18 11:12:01</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3677,34 +3677,34 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>CM-0050 Digital Push Pull Gage</t>
+          <t>CM-0046 Milliohm Meter</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>상태</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>정상</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>미사용</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:33:14</t>
+          <t>2026-08-18 11:11:53</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3729,34 +3729,34 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>CM-0049 버니어켈리퍼스</t>
+          <t>CM-0045 전자저울</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>상태</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>정상</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>미사용</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:31:52</t>
+          <t>2026-08-18 11:11:44</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3781,34 +3781,34 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>CM-0048 디지털 토크 드라이버 셋트</t>
+          <t>CM-0044 Force Gauge</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>상태</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>정상</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>미사용</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:31:23</t>
+          <t>2026-08-18 11:11:17</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3833,34 +3833,34 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>CM-0047 디지털 게이지</t>
+          <t>CM-0043 Digital Push Pull Gage</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>상태</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>정상</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>미사용</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:30:41</t>
+          <t>2026-08-18 11:11:06</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3885,34 +3885,34 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>CM-0046 Milliohm Meter</t>
+          <t>CM-0033 CABLE&amp;HARNESS MULTI TESTER</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>상태</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>정상</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>미사용</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:30:03</t>
+          <t>2026-08-18 11:10:44</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3937,34 +3937,34 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>CM-0045 전자저울</t>
+          <t>CM-0022 광 측정기</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>상태</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>정상</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>미사용</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:29:18</t>
+          <t>2026-08-18 11:10:25</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3994,29 +3994,29 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>CM-0044 Force Gauge</t>
+          <t>CM-0042 HiTESTER</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>설치 위치</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>정상</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>유휴장비보관함</t>
+          <t>미사용</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:29:10</t>
+          <t>2026-08-18 11:09:52</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4041,17 +4041,17 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>수정</t>
+          <t>등록</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>CM-0043 Digital Push Pull Gage</t>
+          <t>CM-0060 Digital Push Pull Gage</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>설치 위치</t>
+          <t/>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -4061,14 +4061,14 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>유휴장비보관함</t>
+          <t>계측기 등록</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:28:52</t>
+          <t>2026-08-18 11:09:03</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>CM-0044 Force Gauge</t>
+          <t>CM-0059 Digital Push Pull Gage</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:28:12</t>
+          <t>2026-08-18 11:08:31</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>CM-0043 Digital Push Pull Gage</t>
+          <t>CM-0058 Digital Push Pull Gage</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4172,7 +4172,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:27:42</t>
+          <t>2026-08-18 11:07:55</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>CM-0042 HiTESTER</t>
+          <t>CM-0057 버니어켈리퍼스</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -4224,7 +4224,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:26:49</t>
+          <t>2026-08-18 11:07:55</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>CM-0041 토크 드라이버</t>
+          <t>CM-0057 버니어켈리퍼스</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>첨부 추가</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -4269,14 +4269,14 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>CM-0057_내외측 켈리퍼(Digamatic Calipers)_251203_대전연구소(25016231-1)_적합성.pdf</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:26:49</t>
+          <t>2026-08-18 11:07:55</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>CM-0041 토크 드라이버</t>
+          <t>CM-0057 버니어켈리퍼스</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4321,14 +4321,14 @@
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>관리번호 CM-0041 260306 - 토크드라이버(CM-E-0033)_연구개발_적합성.pdf</t>
+          <t>CM-0057_내외측 켈리퍼(Digamatic Calipers)_251203_대전연구소(25016231-1).pdf</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:26:49</t>
+          <t>2026-08-18 10:59:48</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4358,12 +4358,12 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>CM-0041 토크 드라이버</t>
+          <t>CM-0056 인두팁 온도계</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>첨부 추가</t>
+          <t/>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -4373,14 +4373,14 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>관리번호 CM-0041 260306 - 토크드라이버(CM-E-0033)_연구개발.pdf</t>
+          <t>계측기 등록</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:00:48</t>
+          <t>2026-08-18 10:58:52</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>CM-0038 레이저길이 측정기</t>
+          <t>CM-0055 디지털테스터</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4432,7 +4432,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:00:48</t>
+          <t>2026-08-18 10:58:01</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4462,12 +4462,12 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>CM-0038 레이저길이 측정기</t>
+          <t>CM-0054 토크 드라이버</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>첨부 추가</t>
+          <t/>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -4477,14 +4477,14 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>CM-0038_레이저길이 측정기_241004_개발실(241002BG14)_적합성.PDF</t>
+          <t>계측기 등록</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:00:48</t>
+          <t>2026-08-18 10:58:01</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>CM-0038 레이저길이 측정기</t>
+          <t>CM-0054 토크 드라이버</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4529,14 +4529,14 @@
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>CM-0038_레이저길이 측정기_241004_개발실(241002BG14).PDF</t>
+          <t>관리번호 CM-0054 260306 - 토크드라이버(457749Q)_연구개발_적합성.pdf</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:58:34</t>
+          <t>2026-08-18 10:58:01</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>CM-0037 1m 곧은자</t>
+          <t>CM-0054 토크 드라이버</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>첨부 추가</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
@@ -4581,14 +4581,14 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>관리번호 CM-0054 260306 - 토크드라이버(457749Q)_연구개발.pdf</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:58:34</t>
+          <t>2026-08-18 10:57:01</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4618,12 +4618,12 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>CM-0037 1m 곧은자</t>
+          <t>CM-0053 전자기 방사선 측정기</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>첨부 추가</t>
+          <t/>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
@@ -4633,14 +4633,14 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>CM-0037_곧은 자 1M_250709_현장(25009308-1)_적합성.pdf</t>
+          <t>계측기 등록</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:58:34</t>
+          <t>2026-08-18 10:56:19</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>CM-0037 1m 곧은자</t>
+          <t>CM-0052 Cable Tester and Digital Multimeter</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>첨부 추가</t>
+          <t/>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
@@ -4685,14 +4685,14 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>CM-0037_곧은 자 1M_250709_현장(25009308-1).pdf</t>
+          <t>계측기 등록</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:57:43</t>
+          <t>2026-08-18 10:55:45</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>CM-0036 30m 줄자</t>
+          <t>CM-0051 휴대용 소음 감지기</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -4744,7 +4744,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:57:43</t>
+          <t>2026-08-18 10:33:45</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>CM-0036 30m 줄자</t>
+          <t>CM-0050 Digital Push Pull Gage</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>첨부 추가</t>
+          <t/>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
@@ -4789,14 +4789,14 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>CM-0036_30m 줄자_250709_현장(25003413-1)_적합성.pdf</t>
+          <t>계측기 등록</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:57:43</t>
+          <t>2026-08-18 10:33:14</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>CM-0036 30m 줄자</t>
+          <t>CM-0049 버니어켈리퍼스</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>첨부 추가</t>
+          <t/>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
@@ -4841,14 +4841,14 @@
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>CM-0036_30m 줄자_250709_현장(25003413-1).pdf</t>
+          <t>계측기 등록</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:56:34</t>
+          <t>2026-08-18 10:31:52</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>CM-0035 5.5m 줄자</t>
+          <t>CM-0048 디지털 토크 드라이버 셋트</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -4900,7 +4900,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:56:34</t>
+          <t>2026-08-18 10:31:23</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4930,12 +4930,12 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>CM-0035 5.5m 줄자</t>
+          <t>CM-0047 디지털 게이지</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>첨부 추가</t>
+          <t/>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
@@ -4945,14 +4945,14 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>CM-0035_5.5m 줄자_250709_현장(25009308-3)_적합성.pdf</t>
+          <t>계측기 등록</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:56:34</t>
+          <t>2026-08-18 10:30:41</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>CM-0035 5.5m 줄자</t>
+          <t>CM-0046 Milliohm Meter</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>첨부 추가</t>
+          <t/>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -4997,14 +4997,14 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>CM-0035_5.5m 줄자_250709_현장(25009308-3).pdf</t>
+          <t>계측기 등록</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:55:12</t>
+          <t>2026-08-18 10:30:03</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>CM-0034 온·습도계</t>
+          <t>CM-0045 전자저울</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:55:12</t>
+          <t>2026-08-18 10:29:18</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -5081,17 +5081,17 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>CM-0034 온·습도계</t>
+          <t>CM-0044 Force Gauge</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>첨부 추가</t>
+          <t>설치 위치</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
@@ -5101,14 +5101,14 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>관리번호 CM-0034_260714- 디지털온도계_AOA실_적합성.pdf</t>
+          <t>유휴장비보관함</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:55:12</t>
+          <t>2026-08-18 10:29:10</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -5133,17 +5133,17 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>CM-0034 온·습도계</t>
+          <t>CM-0043 Digital Push Pull Gage</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>첨부 추가</t>
+          <t>설치 위치</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -5153,14 +5153,14 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>관리번호 CM-0034_260714- 디지털온도계_AOA실.pdf</t>
+          <t>유휴장비보관함</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:53:52</t>
+          <t>2026-08-18 10:28:52</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>CM-0033 CABLE&amp;HARNESS MULTI TESTER</t>
+          <t>CM-0044 Force Gauge</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:52:51</t>
+          <t>2026-08-18 10:28:12</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>CM-0032 Oscilloscope</t>
+          <t>CM-0043 Digital Push Pull Gage</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5264,7 +5264,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:52:51</t>
+          <t>2026-08-18 10:27:42</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>CM-0032 Oscilloscope</t>
+          <t>CM-0042 HiTESTER</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>첨부 추가</t>
+          <t/>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
@@ -5309,14 +5309,14 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>관리번호 CM-0032_260526-Oscilloscope(RTM3004)_대전연구소_적합성.pdf</t>
+          <t>계측기 등록</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:52:51</t>
+          <t>2026-08-18 10:26:49</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>CM-0032 Oscilloscope</t>
+          <t>CM-0041 토크 드라이버</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>첨부 추가</t>
+          <t/>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
@@ -5361,14 +5361,14 @@
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>관리번호 CM-0032_260526-Oscilloscope(RTM3004)_대전연구소.pdf</t>
+          <t>계측기 등록</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:51:15</t>
+          <t>2026-08-18 10:26:49</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>CM-0031 AC Power Supply</t>
+          <t>CM-0041 토크 드라이버</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>첨부 추가</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
@@ -5413,14 +5413,14 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>관리번호 CM-0041 260306 - 토크드라이버(CM-E-0033)_연구개발_적합성.pdf</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:51:15</t>
+          <t>2026-08-18 10:26:49</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>CM-0031 AC Power Supply</t>
+          <t>CM-0041 토크 드라이버</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -5465,14 +5465,14 @@
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>관리번호 CM-0031_260202 - AC Power Supply_AOA실_적합성.pdf</t>
+          <t>관리번호 CM-0041 260306 - 토크드라이버(CM-E-0033)_연구개발.pdf</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:51:15</t>
+          <t>2026-08-18 10:00:48</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5502,12 +5502,12 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>CM-0031 AC Power Supply</t>
+          <t>CM-0038 레이저길이 측정기</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>첨부 추가</t>
+          <t/>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
@@ -5517,14 +5517,14 @@
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>관리번호 CM-0031_260202 - AC Power Supply_AOA실.pdf</t>
+          <t>계측기 등록</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:50:13</t>
+          <t>2026-08-18 10:00:48</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>CM-0030 DC Power Supply</t>
+          <t>CM-0038 레이저길이 측정기</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>첨부 추가</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
@@ -5569,14 +5569,14 @@
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>CM-0038_레이저길이 측정기_241004_개발실(241002BG14)_적합성.PDF</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:50:13</t>
+          <t>2026-08-18 10:00:48</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>CM-0030 DC Power Supply</t>
+          <t>CM-0038 레이저길이 측정기</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5621,14 +5621,14 @@
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>관리번호 CM-0030_260527-Dc Power Supply(E36233A)_대전연구소_적합성.pdf</t>
+          <t>CM-0038_레이저길이 측정기_241004_개발실(241002BG14).PDF</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:50:13</t>
+          <t>2026-08-18 09:58:34</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>CM-0030 DC Power Supply</t>
+          <t>CM-0037 1m 곧은자</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>첨부 추가</t>
+          <t/>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
@@ -5673,14 +5673,14 @@
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>관리번호 CM-0030_260527-Dc Power Supply(E36233A)_대전연구소.pdf</t>
+          <t>계측기 등록</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:48:25</t>
+          <t>2026-08-18 09:58:34</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>CM-0022 광 측정기</t>
+          <t>CM-0037 1m 곧은자</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>첨부 추가</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
@@ -5725,14 +5725,14 @@
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>CM-0037_곧은 자 1M_250709_현장(25009308-1)_적합성.pdf</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:47:38</t>
+          <t>2026-08-18 09:58:34</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>CM-0029 StopWatch</t>
+          <t>CM-0037 1m 곧은자</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>첨부 추가</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
@@ -5777,14 +5777,14 @@
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>CM-0037_곧은 자 1M_250709_현장(25009308-1).pdf</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:47:38</t>
+          <t>2026-08-18 09:57:43</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>CM-0029 StopWatch</t>
+          <t>CM-0036 30m 줄자</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>첨부 추가</t>
+          <t/>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
@@ -5829,14 +5829,14 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>관리번호 CM-0029_260327 - 초시계_StopWatch-_AOA실_적합성.pdf</t>
+          <t>계측기 등록</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:47:38</t>
+          <t>2026-08-18 09:57:43</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5866,7 +5866,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>CM-0029 StopWatch</t>
+          <t>CM-0036 30m 줄자</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -5881,14 +5881,14 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>관리번호 CM-0029_260327 - 초시계_StopWatch-_AOA실.pdf</t>
+          <t>CM-0036_30m 줄자_250709_현장(25003413-1)_적합성.pdf</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:45:50</t>
+          <t>2026-08-18 09:57:43</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>CM-0028 DC Power Supply</t>
+          <t>CM-0036 30m 줄자</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>첨부 추가</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
@@ -5933,14 +5933,14 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>CM-0036_30m 줄자_250709_현장(25003413-1).pdf</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:45:50</t>
+          <t>2026-08-18 09:56:34</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>CM-0028 DC Power Supply</t>
+          <t>CM-0035 5.5m 줄자</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>첨부 추가</t>
+          <t/>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
@@ -5985,14 +5985,14 @@
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>관리번호 CM-0028_260326 - DC POWER SUPPY(GPE-4323)_개발실_적합성.pdf</t>
+          <t>계측기 등록</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:45:50</t>
+          <t>2026-08-18 09:56:34</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>CM-0028 DC Power Supply</t>
+          <t>CM-0035 5.5m 줄자</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6037,14 +6037,14 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>관리번호 CM-0028_260326 - DC POWER SUPPY(GPE-4323)_개발실.pdf</t>
+          <t>CM-0035_5.5m 줄자_250709_현장(25009308-3)_적합성.pdf</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:43:13</t>
+          <t>2026-08-18 09:56:34</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -6074,12 +6074,12 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>CM-0027 Multimeter</t>
+          <t>CM-0035 5.5m 줄자</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>첨부 추가</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
@@ -6089,14 +6089,14 @@
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>CM-0035_5.5m 줄자_250709_현장(25009308-3).pdf</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:43:13</t>
+          <t>2026-08-18 09:55:12</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>CM-0027 Multimeter</t>
+          <t>CM-0034 온·습도계</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>첨부 추가</t>
+          <t/>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
@@ -6141,14 +6141,14 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>관리번호 CM-0027_260327 - DCIGITAK MULTIMETER(MY6006711)_AOA실_적합성.pdf</t>
+          <t>계측기 등록</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:43:13</t>
+          <t>2026-08-18 09:55:12</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>CM-0027 Multimeter</t>
+          <t>CM-0034 온·습도계</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -6193,14 +6193,14 @@
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>관리번호 CM-0027_260327 - DCIGITAK MULTIMETER(MY6006711)_AOA실.pdf</t>
+          <t>관리번호 CM-0034_260714- 디지털온도계_AOA실_적합성.pdf</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:41:32</t>
+          <t>2026-08-18 09:55:12</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -6230,12 +6230,12 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>CM-0026 디지털 온습도계</t>
+          <t>CM-0034 온·습도계</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>첨부 추가</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
@@ -6245,14 +6245,14 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>관리번호 CM-0034_260714- 디지털온도계_AOA실.pdf</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:41:32</t>
+          <t>2026-08-18 09:53:52</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>CM-0026 디지털 온습도계</t>
+          <t>CM-0033 CABLE&amp;HARNESS MULTI TESTER</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>첨부 추가</t>
+          <t/>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
@@ -6297,14 +6297,14 @@
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>CM-0026_디지털 온습도계_251219_생산실1(25017233-2)_적합성.pdf</t>
+          <t>계측기 등록</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:41:32</t>
+          <t>2026-08-18 09:52:51</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>CM-0026 디지털 온습도계</t>
+          <t>CM-0032 Oscilloscope</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>첨부 추가</t>
+          <t/>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
@@ -6349,14 +6349,14 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>CM-0026_디지털 온습도계_251219_생산실1(25017233-2).pdf</t>
+          <t>계측기 등록</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:40:35</t>
+          <t>2026-08-18 09:52:51</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>CM-0025 디지털 온습도계</t>
+          <t>CM-0032 Oscilloscope</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>첨부 추가</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
@@ -6401,14 +6401,14 @@
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>관리번호 CM-0032_260526-Oscilloscope(RTM3004)_대전연구소_적합성.pdf</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:40:35</t>
+          <t>2026-08-18 09:52:51</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>CM-0025 디지털 온습도계</t>
+          <t>CM-0032 Oscilloscope</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6453,14 +6453,14 @@
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>CM-0025_디지털 온습도계_251219_자재실1(25017233-3)_적합성.pdf</t>
+          <t>관리번호 CM-0032_260526-Oscilloscope(RTM3004)_대전연구소.pdf</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:40:35</t>
+          <t>2026-08-18 09:51:15</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>CM-0025 디지털 온습도계</t>
+          <t>CM-0031 AC Power Supply</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>첨부 추가</t>
+          <t/>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
@@ -6505,14 +6505,14 @@
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>CM-0025_디지털 온습도계_251219_자재실1(25017233-3).pdf</t>
+          <t>계측기 등록</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:39:41</t>
+          <t>2026-08-18 09:51:15</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>CM-0024 디지털 온습도계</t>
+          <t>CM-0031 AC Power Supply</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>첨부 추가</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
@@ -6557,14 +6557,14 @@
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>관리번호 CM-0031_260202 - AC Power Supply_AOA실_적합성.pdf</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:39:41</t>
+          <t>2026-08-18 09:51:15</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>CM-0024 디지털 온습도계</t>
+          <t>CM-0031 AC Power Supply</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -6609,14 +6609,14 @@
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>CM-0024_디지털 온습도계_251219_AOA생산실(25017233-1)_적합성.pdf</t>
+          <t>관리번호 CM-0031_260202 - AC Power Supply_AOA실.pdf</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:39:41</t>
+          <t>2026-08-18 09:50:13</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -6646,12 +6646,12 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>CM-0024 디지털 온습도계</t>
+          <t>CM-0030 DC Power Supply</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>첨부 추가</t>
+          <t/>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
@@ -6661,14 +6661,14 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>CM-0024_디지털 온습도계_251219_AOA생산실(25017233-1).pdf</t>
+          <t>계측기 등록</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:38:50</t>
+          <t>2026-08-18 09:50:13</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>CM-0023 디지털 온습도계</t>
+          <t>CM-0030 DC Power Supply</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>첨부 추가</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
@@ -6713,14 +6713,14 @@
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>관리번호 CM-0030_260527-Dc Power Supply(E36233A)_대전연구소_적합성.pdf</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:38:50</t>
+          <t>2026-08-18 09:50:13</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -6750,7 +6750,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>CM-0023 디지털 온습도계</t>
+          <t>CM-0030 DC Power Supply</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -6765,14 +6765,14 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>CM-0023_디지털 온습도계_251219_자재실2(25017233-4)_적합성.pdf</t>
+          <t>관리번호 CM-0030_260527-Dc Power Supply(E36233A)_대전연구소.pdf</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:38:50</t>
+          <t>2026-08-18 09:48:25</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -6802,12 +6802,12 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>CM-0023 디지털 온습도계</t>
+          <t>CM-0022 광 측정기</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>첨부 추가</t>
+          <t/>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
@@ -6817,14 +6817,14 @@
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>CM-0023_디지털 온습도계_251219_자재실2(25017233-4).pdf</t>
+          <t>계측기 등록</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:37:33</t>
+          <t>2026-08-18 09:47:38</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>CM-0021 휘도계</t>
+          <t>CM-0029 StopWatch</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -6876,7 +6876,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:37:33</t>
+          <t>2026-08-18 09:47:38</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>CM-0021 휘도계</t>
+          <t>CM-0029 StopWatch</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -6921,14 +6921,14 @@
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>CM-0021_휘도계_251016_생산실(251015EJ40)_적합성.pdf</t>
+          <t>관리번호 CM-0029_260327 - 초시계_StopWatch-_AOA실_적합성.pdf</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:37:33</t>
+          <t>2026-08-18 09:47:38</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>CM-0021 휘도계</t>
+          <t>CM-0029 StopWatch</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -6973,14 +6973,14 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>CM-0021_휘도계_251016_생산실(251015EJ40).pdf</t>
+          <t>관리번호 CM-0029_260327 - 초시계_StopWatch-_AOA실.pdf</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:36:38</t>
+          <t>2026-08-18 09:45:50</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>CM-0020 전기식 지시저울</t>
+          <t>CM-0028 DC Power Supply</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7032,7 +7032,7 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:36:38</t>
+          <t>2026-08-18 09:45:50</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>CM-0020 전기식 지시저울</t>
+          <t>CM-0028 DC Power Supply</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7077,14 +7077,14 @@
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>CM-0020_전기식 지시저울_251002_현장(25013530-6)_적합성.pdf</t>
+          <t>관리번호 CM-0028_260326 - DC POWER SUPPY(GPE-4323)_개발실_적합성.pdf</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:36:38</t>
+          <t>2026-08-18 09:45:50</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -7114,7 +7114,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>CM-0020 전기식 지시저울</t>
+          <t>CM-0028 DC Power Supply</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -7129,14 +7129,14 @@
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>CM-0020_전기식 지시저울_251002_현장(25013530-6).pdf</t>
+          <t>관리번호 CM-0028_260326 - DC POWER SUPPY(GPE-4323)_개발실.pdf</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:35:39</t>
+          <t>2026-08-18 09:43:13</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>CM-0019 Multimeter</t>
+          <t>CM-0027 Multimeter</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7188,7 +7188,7 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:35:39</t>
+          <t>2026-08-18 09:43:13</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -7218,7 +7218,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>CM-0019 Multimeter</t>
+          <t>CM-0027 Multimeter</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7233,14 +7233,14 @@
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>CM-0019_INSULATION MULTIMETER_251002_현장(25013530-4)_적합성.pdf</t>
+          <t>관리번호 CM-0027_260327 - DCIGITAK MULTIMETER(MY6006711)_AOA실_적합성.pdf</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:35:39</t>
+          <t>2026-08-18 09:43:13</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>CM-0019 Multimeter</t>
+          <t>CM-0027 Multimeter</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7285,14 +7285,14 @@
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>CM-0019_INSULATION MULTIMETER_251002_현장(25013530-4).pdf</t>
+          <t>관리번호 CM-0027_260327 - DCIGITAK MULTIMETER(MY6006711)_AOA실.pdf</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:34:03</t>
+          <t>2026-08-18 09:41:32</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>CM-0018 DC Power Supply</t>
+          <t>CM-0026 디지털 온습도계</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7344,7 +7344,7 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:34:03</t>
+          <t>2026-08-18 09:41:32</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>CM-0018 DC Power Supply</t>
+          <t>CM-0026 디지털 온습도계</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -7389,14 +7389,14 @@
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>CM-0018_DC Power Supply_251002_AOA생산실(25013530-7)_적합성.pdf</t>
+          <t>CM-0026_디지털 온습도계_251219_생산실1(25017233-2)_적합성.pdf</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:34:03</t>
+          <t>2026-08-18 09:41:32</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>CM-0018 DC Power Supply</t>
+          <t>CM-0026 디지털 온습도계</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -7441,14 +7441,14 @@
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>CM-0018_DC Power Supply_251002_AOA생산실(25013530-7).pdf</t>
+          <t>CM-0026_디지털 온습도계_251219_생산실1(25017233-2).pdf</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:31:55</t>
+          <t>2026-08-18 09:40:35</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>CM-0017 mΩ HiTESTER</t>
+          <t>CM-0025 디지털 온습도계</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7500,7 +7500,7 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:31:55</t>
+          <t>2026-08-18 09:40:35</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>CM-0017 mΩ HiTESTER</t>
+          <t>CM-0025 디지털 온습도계</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -7545,14 +7545,14 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>관리번호 CM-0017_260805_ mΩ HiTESTER_현장_적합성.pdf</t>
+          <t>CM-0025_디지털 온습도계_251219_자재실1(25017233-3)_적합성.pdf</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:31:55</t>
+          <t>2026-08-18 09:40:35</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>CM-0017 mΩ HiTESTER</t>
+          <t>CM-0025 디지털 온습도계</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7597,14 +7597,14 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>관리번호 CM-0017_260805_ mΩ HiTESTER_현장 .pdf</t>
+          <t>CM-0025_디지털 온습도계_251219_자재실1(25017233-3).pdf</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:29:41</t>
+          <t>2026-08-18 09:39:41</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>CM-0016 광조도계</t>
+          <t>CM-0024 디지털 온습도계</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7656,7 +7656,7 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:29:41</t>
+          <t>2026-08-18 09:39:41</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>CM-0016 광조도계</t>
+          <t>CM-0024 디지털 온습도계</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7701,14 +7701,14 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>CM-0016_광조도계_250903_개발실(25021404-1)_적합성.pdf</t>
+          <t>CM-0024_디지털 온습도계_251219_AOA생산실(25017233-1)_적합성.pdf</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:29:41</t>
+          <t>2026-08-18 09:39:41</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>CM-0016 광조도계</t>
+          <t>CM-0024 디지털 온습도계</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -7753,14 +7753,14 @@
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>CM-0016_광조도계_250903_개발실(25021404-1).pdf</t>
+          <t>CM-0024_디지털 온습도계_251219_AOA생산실(25017233-1).pdf</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:28:42</t>
+          <t>2026-08-18 09:38:50</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>CM-0015 휘도계</t>
+          <t>CM-0023 디지털 온습도계</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -7812,7 +7812,7 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:28:42</t>
+          <t>2026-08-18 09:38:50</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>CM-0015 휘도계</t>
+          <t>CM-0023 디지털 온습도계</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -7857,14 +7857,14 @@
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>CM-0015_휘도계(LUMINANCE COLORI METER)_250909_생산실(250903EM64)_적합성.pdf</t>
+          <t>CM-0023_디지털 온습도계_251219_자재실2(25017233-4)_적합성.pdf</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:28:42</t>
+          <t>2026-08-18 09:38:50</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
@@ -7894,7 +7894,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>CM-0015 휘도계</t>
+          <t>CM-0023 디지털 온습도계</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -7909,14 +7909,14 @@
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>CM-0015_휘도계(LUMINANCE COLORI METER)_250909_생산실(250903EM64).pdf</t>
+          <t>CM-0023_디지털 온습도계_251219_자재실2(25017233-4).pdf</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:27:44</t>
+          <t>2026-08-18 09:37:33</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
@@ -7946,7 +7946,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>CM-0014 듀얼축 각도기</t>
+          <t>CM-0021 휘도계</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -7968,7 +7968,7 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:27:44</t>
+          <t>2026-08-18 09:37:33</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>CM-0014 듀얼축 각도기</t>
+          <t>CM-0021 휘도계</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -8013,14 +8013,14 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>CM-0014_각도 정규(듀얼축 각도기)_250901_개발실(25011747-11)_적합성.pdf</t>
+          <t>CM-0021_휘도계_251016_생산실(251015EJ40)_적합성.pdf</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:27:44</t>
+          <t>2026-08-18 09:37:33</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>CM-0014 듀얼축 각도기</t>
+          <t>CM-0021 휘도계</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -8065,14 +8065,14 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>CM-0014_각도 정규(듀얼축 각도기)_250901_개발실(25011747-11).pdf</t>
+          <t>CM-0021_휘도계_251016_생산실(251015EJ40).pdf</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:26:09</t>
+          <t>2026-08-18 09:36:38</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
@@ -8102,7 +8102,7 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>CM-0013 버니어켈리퍼스</t>
+          <t>CM-0020 전기식 지시저울</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -8124,7 +8124,7 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:26:09</t>
+          <t>2026-08-18 09:36:38</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>CM-0013 버니어켈리퍼스</t>
+          <t>CM-0020 전기식 지시저울</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8169,14 +8169,14 @@
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>CM-0013_내외측캘리퍼(버니어캐리퍼스)_251013_개발실(25013530-2)_적합성.pdf</t>
+          <t>CM-0020_전기식 지시저울_251002_현장(25013530-6)_적합성.pdf</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:26:09</t>
+          <t>2026-08-18 09:36:38</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
@@ -8206,7 +8206,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>CM-0013 버니어켈리퍼스</t>
+          <t>CM-0020 전기식 지시저울</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8221,14 +8221,14 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>CM-0013_내외측캘리퍼(버니어캐리퍼스)_251013_개발실(25013530-2).pdf</t>
+          <t>CM-0020_전기식 지시저울_251002_현장(25013530-6).pdf</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:25:11</t>
+          <t>2026-08-18 09:35:39</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>CM-0012 버니어켈리퍼스</t>
+          <t>CM-0019 Multimeter</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -8280,7 +8280,7 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:25:11</t>
+          <t>2026-08-18 09:35:39</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>CM-0012 버니어켈리퍼스</t>
+          <t>CM-0019 Multimeter</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -8325,14 +8325,14 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>CM-0012_내외측캘리퍼(버니어캐리퍼스)_250901_개발실(25011747-8)_적합성.pdf</t>
+          <t>CM-0019_INSULATION MULTIMETER_251002_현장(25013530-4)_적합성.pdf</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:25:11</t>
+          <t>2026-08-18 09:35:39</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
@@ -8362,7 +8362,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>CM-0012 버니어켈리퍼스</t>
+          <t>CM-0019 Multimeter</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -8377,14 +8377,14 @@
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>CM-0012_내외측캘리퍼(버니어캐리퍼스)_250901_개발실(25011747-8).pdf</t>
+          <t>CM-0019_INSULATION MULTIMETER_251002_현장(25013530-4).pdf</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:24:13</t>
+          <t>2026-08-18 09:34:03</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>CM-0011 버니어켈리퍼스</t>
+          <t>CM-0018 DC Power Supply</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
@@ -8436,7 +8436,7 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:24:13</t>
+          <t>2026-08-18 09:34:03</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>CM-0011 버니어켈리퍼스</t>
+          <t>CM-0018 DC Power Supply</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -8481,14 +8481,14 @@
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
-          <t>CM-0011_내외측캘리퍼(버니어캐리퍼스)_250901_개발실(25011747-9)_적합성.pdf</t>
+          <t>CM-0018_DC Power Supply_251002_AOA생산실(25013530-7)_적합성.pdf</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:24:13</t>
+          <t>2026-08-18 09:34:03</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>CM-0011 버니어켈리퍼스</t>
+          <t>CM-0018 DC Power Supply</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
@@ -8533,14 +8533,14 @@
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>CM-0011_내외측캘리퍼(버니어캐리퍼스)_250901_개발실(25011747-9).pdf</t>
+          <t>CM-0018_DC Power Supply_251002_AOA생산실(25013530-7).pdf</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:23:00</t>
+          <t>2026-08-18 09:31:55</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>CM-0010 온도측정기</t>
+          <t>CM-0017 mΩ HiTESTER</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
@@ -8592,7 +8592,7 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:23:00</t>
+          <t>2026-08-18 09:31:55</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
@@ -8622,7 +8622,7 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>CM-0010 온도측정기</t>
+          <t>CM-0017 mΩ HiTESTER</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -8637,14 +8637,14 @@
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>CM-0010_복사온도계(온도측정기)_250912_개발실(25012472-1)_적합성.pdf</t>
+          <t>관리번호 CM-0017_260805_ mΩ HiTESTER_현장_적합성.pdf</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:23:00</t>
+          <t>2026-08-18 09:31:55</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>CM-0010 온도측정기</t>
+          <t>CM-0017 mΩ HiTESTER</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -8689,14 +8689,14 @@
       </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
-          <t>CM-0010_복사온도계(온도측정기)_250912_개발실(25012472-1).pdf</t>
+          <t>관리번호 CM-0017_260805_ mΩ HiTESTER_현장 .pdf</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:20:42</t>
+          <t>2026-08-18 09:29:41</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>CM-0008 Milliohm Meter</t>
+          <t>CM-0016 광조도계</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -8748,7 +8748,7 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:20:42</t>
+          <t>2026-08-18 09:29:41</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
@@ -8778,7 +8778,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>CM-0008 Milliohm Meter</t>
+          <t>CM-0016 광조도계</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -8793,14 +8793,14 @@
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>CM-0008_Milliohm Meter_250829_AOA생산실_(25011747-3)_적합성.pdf</t>
+          <t>CM-0016_광조도계_250903_개발실(25021404-1)_적합성.pdf</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:20:42</t>
+          <t>2026-08-18 09:29:41</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>CM-0008 Milliohm Meter</t>
+          <t>CM-0016 광조도계</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -8845,14 +8845,14 @@
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>CM-0008_Milliohm Meter_250829_AOA생산실_(25011747-3).pdf</t>
+          <t>CM-0016_광조도계_250903_개발실(25021404-1).pdf</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:19:48</t>
+          <t>2026-08-18 09:28:42</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>CM-0007 TRUE RMS Multimeter</t>
+          <t>CM-0015 휘도계</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -8904,7 +8904,7 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:19:48</t>
+          <t>2026-08-18 09:28:42</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>CM-0007 TRUE RMS Multimeter</t>
+          <t>CM-0015 휘도계</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -8949,14 +8949,14 @@
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>CM-0007_TRUE RMS Multimeter_250829_개발실(25011747-4)_적합성.pdf</t>
+          <t>CM-0015_휘도계(LUMINANCE COLORI METER)_250909_생산실(250903EM64)_적합성.pdf</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:19:48</t>
+          <t>2026-08-18 09:28:42</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>CM-0007 TRUE RMS Multimeter</t>
+          <t>CM-0015 휘도계</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -9001,14 +9001,14 @@
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>CM-0007_TRUE RMS Multimeter_250829_개발실(25011747-4).pdf</t>
+          <t>CM-0015_휘도계(LUMINANCE COLORI METER)_250909_생산실(250903EM64).pdf</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:18:31</t>
+          <t>2026-08-18 09:27:44</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>CM-0006 TRUE RMS Multimeter</t>
+          <t>CM-0014 듀얼축 각도기</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -9060,7 +9060,7 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:18:31</t>
+          <t>2026-08-18 09:27:44</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
@@ -9090,7 +9090,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>CM-0006 TRUE RMS Multimeter</t>
+          <t>CM-0014 듀얼축 각도기</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -9105,14 +9105,14 @@
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>CM-0006_TRUE RMS Multimeter_250829_ 개발실(25011747-5)_적합성.pdf</t>
+          <t>CM-0014_각도 정규(듀얼축 각도기)_250901_개발실(25011747-11)_적합성.pdf</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:18:31</t>
+          <t>2026-08-18 09:27:44</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>CM-0006 TRUE RMS Multimeter</t>
+          <t>CM-0014 듀얼축 각도기</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -9157,14 +9157,14 @@
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>CM-0006_TRUE RMS Multimeter_250829_ 개발실(25011747-5).pdf</t>
+          <t>CM-0014_각도 정규(듀얼축 각도기)_250901_개발실(25011747-11).pdf</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:17:16</t>
+          <t>2026-08-18 09:26:09</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
@@ -9189,34 +9189,34 @@
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>수정</t>
+          <t>등록</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>CM-0005 온·습도계</t>
+          <t>CM-0013 버니어켈리퍼스</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>계측기명</t>
+          <t/>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>온습도계</t>
+          <t/>
         </is>
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>온·습도계</t>
+          <t>계측기 등록</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:17:00</t>
+          <t>2026-08-18 09:26:09</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
@@ -9246,12 +9246,12 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>CM-0005 온습도계</t>
+          <t>CM-0013 버니어켈리퍼스</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>첨부 추가</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
@@ -9261,14 +9261,14 @@
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>CM-0013_내외측캘리퍼(버니어캐리퍼스)_251013_개발실(25013530-2)_적합성.pdf</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:17:00</t>
+          <t>2026-08-18 09:26:09</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
@@ -9298,7 +9298,7 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>CM-0005 온습도계</t>
+          <t>CM-0013 버니어켈리퍼스</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -9313,14 +9313,14 @@
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>CM-0005_온습도계_251014_현장(25013530-3)_적합성.pdf</t>
+          <t>CM-0013_내외측캘리퍼(버니어캐리퍼스)_251013_개발실(25013530-2).pdf</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:17:00</t>
+          <t>2026-08-18 09:25:11</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
@@ -9350,12 +9350,12 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>CM-0005 온습도계</t>
+          <t>CM-0012 버니어켈리퍼스</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>첨부 추가</t>
+          <t/>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
@@ -9365,14 +9365,14 @@
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>CM-0005_온습도계_251014_현장(25013530-3).pdf</t>
+          <t>계측기 등록</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:15:36</t>
+          <t>2026-08-18 09:25:11</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
@@ -9402,12 +9402,12 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>CM-0004 온·습도계</t>
+          <t>CM-0012 버니어켈리퍼스</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>첨부 추가</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr">
@@ -9417,14 +9417,14 @@
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>CM-0012_내외측캘리퍼(버니어캐리퍼스)_250901_개발실(25011747-8)_적합성.pdf</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:15:36</t>
+          <t>2026-08-18 09:25:11</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>CM-0004 온·습도계</t>
+          <t>CM-0012 버니어켈리퍼스</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
@@ -9469,14 +9469,14 @@
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>CM-0004_온습도계_250829_자재실(25011747-7)_적합성.pdf</t>
+          <t>CM-0012_내외측캘리퍼(버니어캐리퍼스)_250901_개발실(25011747-8).pdf</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:15:36</t>
+          <t>2026-08-18 09:24:13</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>CM-0004 온·습도계</t>
+          <t>CM-0011 버니어켈리퍼스</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>첨부 추가</t>
+          <t/>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr">
@@ -9521,14 +9521,14 @@
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>CM-0004_온습도계_250829_자재실(25011747-7).pdf</t>
+          <t>계측기 등록</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:13:28</t>
+          <t>2026-08-18 09:24:13</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>CM-0003 Oscilloscope</t>
+          <t>CM-0011 버니어켈리퍼스</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>첨부 추가</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
@@ -9573,14 +9573,14 @@
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>CM-0011_내외측캘리퍼(버니어캐리퍼스)_250901_개발실(25011747-9)_적합성.pdf</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:13:28</t>
+          <t>2026-08-18 09:24:13</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
@@ -9610,7 +9610,7 @@
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>CM-0003 Oscilloscope</t>
+          <t>CM-0011 버니어켈리퍼스</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
@@ -9625,14 +9625,14 @@
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>CM-0003_Oscilloscope_250919_현장(WO-01196944)_적합성.pdf</t>
+          <t>CM-0011_내외측캘리퍼(버니어캐리퍼스)_250901_개발실(25011747-9).pdf</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:13:28</t>
+          <t>2026-08-18 09:23:00</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
@@ -9662,12 +9662,12 @@
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>CM-0003 Oscilloscope</t>
+          <t>CM-0010 온도측정기</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>첨부 추가</t>
+          <t/>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
@@ -9677,14 +9677,14 @@
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>CM-0003_Oscilloscope_250919_현장(WO-01196944).pdf</t>
+          <t>계측기 등록</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:09:52</t>
+          <t>2026-08-18 09:23:00</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>CM-0002 DC Power Supply</t>
+          <t>CM-0010 온도측정기</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>첨부 추가</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
@@ -9729,14 +9729,14 @@
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>CM-0010_복사온도계(온도측정기)_250912_개발실(25012472-1)_적합성.pdf</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:09:52</t>
+          <t>2026-08-18 09:23:00</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>CM-0002 DC Power Supply</t>
+          <t>CM-0010 온도측정기</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
@@ -9781,14 +9781,14 @@
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>CM-0002_DC Power Supply_250829_개발실(25011747-2)_적합성.pdf</t>
+          <t>CM-0010_복사온도계(온도측정기)_250912_개발실(25012472-1).pdf</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:09:52</t>
+          <t>2026-08-18 09:20:42</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>CM-0002 DC Power Supply</t>
+          <t>CM-0008 Milliohm Meter</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>첨부 추가</t>
+          <t/>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr">
@@ -9833,14 +9833,14 @@
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>CM-0002_DC Power Supply_250829_개발실(25011747-2).pdf</t>
+          <t>계측기 등록</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:07:26</t>
+          <t>2026-08-18 09:20:42</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
@@ -9870,12 +9870,12 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>CM-0001 DC Power Supply</t>
+          <t>CM-0008 Milliohm Meter</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>첨부 추가</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
@@ -9885,14 +9885,14 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>계측기 등록</t>
+          <t>CM-0008_Milliohm Meter_250829_AOA생산실_(25011747-3)_적합성.pdf</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:01:07</t>
+          <t>2026-08-18 09:20:42</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
@@ -9917,34 +9917,34 @@
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>수정</t>
+          <t>등록</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>CM-0009 적외선 온도계</t>
+          <t>CM-0008 Milliohm Meter</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>사용 부서</t>
+          <t>첨부 추가</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t/>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>CM-0008_Milliohm Meter_250829_AOA생산실_(25011747-3).pdf</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 09:01:07</t>
+          <t>2026-08-18 09:19:48</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
@@ -9969,17 +9969,17 @@
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>수정</t>
+          <t>등록</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>CM-0009 적외선 온도계</t>
+          <t>CM-0007 TRUE RMS Multimeter</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>설치 위치</t>
+          <t/>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
@@ -9989,14 +9989,14 @@
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>계측기 등록</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 08:55:35</t>
+          <t>2026-08-18 09:19:48</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
@@ -10021,17 +10021,17 @@
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>수정</t>
+          <t>등록</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>CM-0009 적외선 온도계</t>
+          <t>CM-0007 TRUE RMS Multimeter</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>사용 부서</t>
+          <t>첨부 추가</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
@@ -10041,57 +10041,1149 @@
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>CM-0007_TRUE RMS Multimeter_250829_개발실(25011747-4)_적합성.pdf</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
+          <t>2026-08-18 09:19:48</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>주식회사 카프마이크로</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>박준영</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>jypark@caphmicro.com</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>계측기 통합 대장</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>등록</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>CM-0007 TRUE RMS Multimeter</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>첨부 추가</t>
+        </is>
+      </c>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J192" s="2" t="inlineStr">
+        <is>
+          <t>CM-0007_TRUE RMS Multimeter_250829_개발실(25011747-4).pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:18:31</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>주식회사 카프마이크로</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>박준영</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>jypark@caphmicro.com</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>계측기 통합 대장</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>등록</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>CM-0006 TRUE RMS Multimeter</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J193" s="2" t="inlineStr">
+        <is>
+          <t>계측기 등록</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:18:31</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>주식회사 카프마이크로</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>박준영</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>jypark@caphmicro.com</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>계측기 통합 대장</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>등록</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>CM-0006 TRUE RMS Multimeter</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>첨부 추가</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J194" s="2" t="inlineStr">
+        <is>
+          <t>CM-0006_TRUE RMS Multimeter_250829_ 개발실(25011747-5)_적합성.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:18:31</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>주식회사 카프마이크로</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>박준영</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>jypark@caphmicro.com</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>계측기 통합 대장</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>등록</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>CM-0006 TRUE RMS Multimeter</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>첨부 추가</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J195" s="2" t="inlineStr">
+        <is>
+          <t>CM-0006_TRUE RMS Multimeter_250829_ 개발실(25011747-5).pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:17:16</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>주식회사 카프마이크로</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>박준영</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>jypark@caphmicro.com</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>계측기 통합 대장</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>CM-0005 온·습도계</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>계측기명</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>온습도계</t>
+        </is>
+      </c>
+      <c r="J196" s="2" t="inlineStr">
+        <is>
+          <t>온·습도계</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:17:00</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>주식회사 카프마이크로</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>박준영</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>jypark@caphmicro.com</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>계측기 통합 대장</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>등록</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>CM-0005 온습도계</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J197" s="2" t="inlineStr">
+        <is>
+          <t>계측기 등록</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:17:00</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>주식회사 카프마이크로</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>박준영</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>jypark@caphmicro.com</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>계측기 통합 대장</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>등록</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>CM-0005 온습도계</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>첨부 추가</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J198" s="2" t="inlineStr">
+        <is>
+          <t>CM-0005_온습도계_251014_현장(25013530-3)_적합성.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:17:00</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>주식회사 카프마이크로</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>박준영</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>jypark@caphmicro.com</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>계측기 통합 대장</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>등록</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>CM-0005 온습도계</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>첨부 추가</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J199" s="2" t="inlineStr">
+        <is>
+          <t>CM-0005_온습도계_251014_현장(25013530-3).pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:15:36</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>주식회사 카프마이크로</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>박준영</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>jypark@caphmicro.com</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>계측기 통합 대장</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>등록</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>CM-0004 온·습도계</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J200" s="2" t="inlineStr">
+        <is>
+          <t>계측기 등록</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:15:36</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>주식회사 카프마이크로</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>박준영</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>jypark@caphmicro.com</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>계측기 통합 대장</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>등록</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>CM-0004 온·습도계</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>첨부 추가</t>
+        </is>
+      </c>
+      <c r="I201" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J201" s="2" t="inlineStr">
+        <is>
+          <t>CM-0004_온습도계_250829_자재실(25011747-7)_적합성.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:15:36</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>주식회사 카프마이크로</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>박준영</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>jypark@caphmicro.com</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>계측기 통합 대장</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>등록</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>CM-0004 온·습도계</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>첨부 추가</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J202" s="2" t="inlineStr">
+        <is>
+          <t>CM-0004_온습도계_250829_자재실(25011747-7).pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:13:28</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>주식회사 카프마이크로</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>박준영</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>jypark@caphmicro.com</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>계측기 통합 대장</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>등록</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>CM-0003 Oscilloscope</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I203" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J203" s="2" t="inlineStr">
+        <is>
+          <t>계측기 등록</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:13:28</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>주식회사 카프마이크로</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>박준영</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>jypark@caphmicro.com</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>계측기 통합 대장</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>등록</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>CM-0003 Oscilloscope</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>첨부 추가</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J204" s="2" t="inlineStr">
+        <is>
+          <t>CM-0003_Oscilloscope_250919_현장(WO-01196944)_적합성.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:13:28</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>주식회사 카프마이크로</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>박준영</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>jypark@caphmicro.com</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>계측기 통합 대장</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>등록</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>CM-0003 Oscilloscope</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>첨부 추가</t>
+        </is>
+      </c>
+      <c r="I205" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J205" s="2" t="inlineStr">
+        <is>
+          <t>CM-0003_Oscilloscope_250919_현장(WO-01196944).pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:09:52</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>주식회사 카프마이크로</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>박준영</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>jypark@caphmicro.com</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>계측기 통합 대장</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>등록</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>CM-0002 DC Power Supply</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J206" s="2" t="inlineStr">
+        <is>
+          <t>계측기 등록</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:09:52</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>주식회사 카프마이크로</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>박준영</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>jypark@caphmicro.com</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>계측기 통합 대장</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>등록</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>CM-0002 DC Power Supply</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>첨부 추가</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J207" s="2" t="inlineStr">
+        <is>
+          <t>CM-0002_DC Power Supply_250829_개발실(25011747-2)_적합성.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:09:52</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>주식회사 카프마이크로</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>박준영</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>jypark@caphmicro.com</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>계측기 통합 대장</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>등록</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>CM-0002 DC Power Supply</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>첨부 추가</t>
+        </is>
+      </c>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J208" s="2" t="inlineStr">
+        <is>
+          <t>CM-0002_DC Power Supply_250829_개발실(25011747-2).pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:07:26</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>주식회사 카프마이크로</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>박준영</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>jypark@caphmicro.com</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>계측기 통합 대장</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>등록</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>CM-0001 DC Power Supply</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J209" s="2" t="inlineStr">
+        <is>
+          <t>계측기 등록</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:01:07</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>주식회사 카프마이크로</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>박준영</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>jypark@caphmicro.com</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>계측기 통합 대장</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>CM-0009 적외선 온도계</t>
+        </is>
+      </c>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t>사용 부서</t>
+        </is>
+      </c>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="J210" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:01:07</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>주식회사 카프마이크로</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>박준영</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>jypark@caphmicro.com</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>계측기 통합 대장</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>CM-0009 적외선 온도계</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>설치 위치</t>
+        </is>
+      </c>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J211" s="2" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 08:55:35</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>주식회사 카프마이크로</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>박준영</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>jypark@caphmicro.com</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>계측기 통합 대장</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>CM-0009 적외선 온도계</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>사용 부서</t>
+        </is>
+      </c>
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J212" s="2" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
           <t>2026-08-18 08:34:49</t>
         </is>
       </c>
-      <c r="B192" s="2" t="inlineStr">
-        <is>
-          <t>주식회사 카프마이크로</t>
-        </is>
-      </c>
-      <c r="C192" s="2" t="inlineStr">
-        <is>
-          <t>박준영</t>
-        </is>
-      </c>
-      <c r="D192" s="2" t="inlineStr">
-        <is>
-          <t>jypark@caphmicro.com</t>
-        </is>
-      </c>
-      <c r="E192" s="2" t="inlineStr">
-        <is>
-          <t>계측기 통합 대장</t>
-        </is>
-      </c>
-      <c r="F192" s="2" t="inlineStr">
-        <is>
-          <t>등록</t>
-        </is>
-      </c>
-      <c r="G192" s="2" t="inlineStr">
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>주식회사 카프마이크로</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>박준영</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>jypark@caphmicro.com</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>계측기 통합 대장</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>등록</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
         <is>
           <t>CM-0009 적외선 온도계</t>
         </is>
       </c>
-      <c r="H192" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I192" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J192" s="2" t="inlineStr">
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J213" s="2" t="inlineStr">
         <is>
           <t>계측기 등록</t>
         </is>
